--- a/Excel/jamesnocode.xlsx
+++ b/Excel/jamesnocode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>34935</v>
+        <v>42136</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10787</v>
+        <v>20958</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7466</v>
+        <v>10156</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -553,28 +553,118 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>V6x0XNsrjQE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Learn 90% of DeepSeek in 30 minutes (Full Tutorial)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6158</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0:29:43</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tQM6qoB9P0k</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>OpenCode Tutorial for Beginners: Master Rules, Skills &amp; MCP (In 20 Minutes)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5363</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0:19:58</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>DwikL8QBcDU</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Codex vs. OpenCode (2026): The Truth After Real Testing</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>2271</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D7" t="n">
+        <v>5129</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>0:36:45</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>vO1g1SISryw</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Build Awesome NoCode Apps with DeepSeek (Full Chat App Demo)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1830</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0:26:19</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
